--- a/results/class_sensitivity/recurrence_vs_hsp90_selectivity.xlsx
+++ b/results/class_sensitivity/recurrence_vs_hsp90_selectivity.xlsx
@@ -446,7 +446,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.4622470552703111</v>
+        <v>0.4027484143763214</v>
       </c>
     </row>
     <row r="4">
@@ -456,7 +456,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.001804377183020941</v>
+        <v>0.007414613386193692</v>
       </c>
     </row>
     <row r="5">
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1565305764062561</v>
+        <v>0.08391401629922249</v>
       </c>
     </row>
     <row r="8">
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6931747862751243</v>
+        <v>0.6432836905889364</v>
       </c>
     </row>
     <row r="9">
@@ -560,13 +560,13 @@
         <v>-0.1786272139903385</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3076923076923077</v>
+        <v>0.3205128205128205</v>
       </c>
       <c r="D2" t="n">
         <v>0.3461538461538461</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.03846153846153844</v>
+        <v>-0.02564102564102566</v>
       </c>
     </row>
     <row r="3">
@@ -598,13 +598,13 @@
         <v>-0.2094323762561981</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6499999999999999</v>
       </c>
       <c r="D4" t="n">
         <v>0.5333333333333333</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1333333333333333</v>
+        <v>0.1166666666666666</v>
       </c>
     </row>
     <row r="5">
@@ -674,13 +674,13 @@
         <v>-0.2183080445642374</v>
       </c>
       <c r="C8" t="n">
-        <v>0.6793381037567083</v>
+        <v>0.6279069767441861</v>
       </c>
       <c r="D8" t="n">
         <v>0.3333333333333333</v>
       </c>
       <c r="E8" t="n">
-        <v>0.346004770423375</v>
+        <v>0.2945736434108527</v>
       </c>
     </row>
     <row r="9">
@@ -693,13 +693,13 @@
         <v>-0.1662653967408163</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6</v>
+        <v>0.5391472868217054</v>
       </c>
       <c r="D9" t="n">
         <v>0.5172413793103449</v>
       </c>
       <c r="E9" t="n">
-        <v>0.08275862068965512</v>
+        <v>0.02190590751136057</v>
       </c>
     </row>
     <row r="10">
@@ -769,13 +769,13 @@
         <v>-0.2235656201793519</v>
       </c>
       <c r="C13" t="n">
-        <v>0.7897435897435897</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="D13" t="n">
         <v>0.6333333333333333</v>
       </c>
       <c r="E13" t="n">
-        <v>0.1564102564102564</v>
+        <v>0.09999999999999998</v>
       </c>
     </row>
     <row r="14">
@@ -788,13 +788,13 @@
         <v>-0.2064610311547386</v>
       </c>
       <c r="C14" t="n">
-        <v>0.7441860465116279</v>
+        <v>0.772093023255814</v>
       </c>
       <c r="D14" t="n">
         <v>0.5666666666666667</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1775193798449612</v>
+        <v>0.2054263565891473</v>
       </c>
     </row>
     <row r="15">
@@ -807,13 +807,13 @@
         <v>-0.2082082076743421</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2583333333333333</v>
+        <v>0.3</v>
       </c>
       <c r="D15" t="n">
         <v>0.5</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.2416666666666667</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="16">
@@ -864,13 +864,13 @@
         <v>-0.1414054398988475</v>
       </c>
       <c r="C18" t="n">
-        <v>0.6976744186046512</v>
+        <v>0.7626303127506014</v>
       </c>
       <c r="D18" t="n">
         <v>0.4333333333333333</v>
       </c>
       <c r="E18" t="n">
-        <v>0.2643410852713178</v>
+        <v>0.3292969794172681</v>
       </c>
     </row>
     <row r="19">
@@ -883,13 +883,13 @@
         <v>-0.1783653544666676</v>
       </c>
       <c r="C19" t="n">
-        <v>0.7666666666666667</v>
+        <v>0.7404761904761905</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6511627906976745</v>
+        <v>0.6525044722719142</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1155038759689923</v>
+        <v>0.08797171820427629</v>
       </c>
     </row>
     <row r="20">
@@ -902,13 +902,13 @@
         <v>-0.2272999068630794</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2142857142857143</v>
+        <v>0.2562015503875969</v>
       </c>
       <c r="D20" t="n">
         <v>0.3666666666666666</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.1523809523809524</v>
+        <v>-0.1104651162790697</v>
       </c>
     </row>
     <row r="21">
@@ -940,13 +940,13 @@
         <v>-0.2357862821744499</v>
       </c>
       <c r="C22" t="n">
-        <v>0.1162790697674419</v>
+        <v>0.2</v>
       </c>
       <c r="D22" t="n">
         <v>0.3571428571428572</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.2408637873754153</v>
+        <v>-0.1571428571428571</v>
       </c>
     </row>
     <row r="23">
@@ -959,13 +959,13 @@
         <v>-0.1928960493937777</v>
       </c>
       <c r="C23" t="n">
-        <v>0.4523809523809524</v>
+        <v>0.296551724137931</v>
       </c>
       <c r="D23" t="n">
         <v>0.4</v>
       </c>
       <c r="E23" t="n">
-        <v>0.05238095238095236</v>
+        <v>-0.103448275862069</v>
       </c>
     </row>
     <row r="24">
@@ -978,13 +978,13 @@
         <v>-0.1891070006869582</v>
       </c>
       <c r="C24" t="n">
-        <v>0.6923076923076923</v>
+        <v>0.6252236135957066</v>
       </c>
       <c r="D24" t="n">
         <v>0.6666666666666666</v>
       </c>
       <c r="E24" t="n">
-        <v>0.02564102564102566</v>
+        <v>-0.04144305307096008</v>
       </c>
     </row>
     <row r="25">
@@ -997,13 +997,13 @@
         <v>-0.1679123265606992</v>
       </c>
       <c r="C25" t="n">
-        <v>0.7690476190476191</v>
+        <v>0.6511627906976745</v>
       </c>
       <c r="D25" t="n">
         <v>0.5</v>
       </c>
       <c r="E25" t="n">
-        <v>0.2690476190476191</v>
+        <v>0.1511627906976745</v>
       </c>
     </row>
     <row r="26">
@@ -1016,13 +1016,13 @@
         <v>-0.2002121226750436</v>
       </c>
       <c r="C26" t="n">
-        <v>0.4666666666666667</v>
+        <v>0.4775193798449612</v>
       </c>
       <c r="D26" t="n">
         <v>0.5666666666666667</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.09999999999999998</v>
+        <v>-0.08914728682170542</v>
       </c>
     </row>
     <row r="27">
@@ -1038,10 +1038,10 @@
         <v>0.2</v>
       </c>
       <c r="D27" t="n">
-        <v>0.462962962962963</v>
+        <v>0.4642857142857143</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.262962962962963</v>
+        <v>-0.2642857142857143</v>
       </c>
     </row>
     <row r="28">
@@ -1054,13 +1054,13 @@
         <v>-0.1820048265378515</v>
       </c>
       <c r="C28" t="n">
-        <v>0.1785714285714286</v>
+        <v>0.1726190476190476</v>
       </c>
       <c r="D28" t="n">
         <v>0.396551724137931</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.2179802955665025</v>
+        <v>-0.2239326765188834</v>
       </c>
     </row>
     <row r="29">
@@ -1092,13 +1092,13 @@
         <v>-0.1998464016445489</v>
       </c>
       <c r="C30" t="n">
-        <v>0.3928571428571428</v>
+        <v>0.3964285714285715</v>
       </c>
       <c r="D30" t="n">
-        <v>0.3908730158730159</v>
+        <v>0.3888888888888889</v>
       </c>
       <c r="E30" t="n">
-        <v>0.001984126984126977</v>
+        <v>0.007539682539682568</v>
       </c>
     </row>
     <row r="31">
@@ -1111,13 +1111,13 @@
         <v>-0.205184187788136</v>
       </c>
       <c r="C31" t="n">
-        <v>0.8023255813953489</v>
+        <v>0.7666666666666667</v>
       </c>
       <c r="D31" t="n">
         <v>0.5769230769230769</v>
       </c>
       <c r="E31" t="n">
-        <v>0.2254025044722721</v>
+        <v>0.1897435897435898</v>
       </c>
     </row>
     <row r="32">
@@ -1130,13 +1130,13 @@
         <v>-0.184285453771279</v>
       </c>
       <c r="C32" t="n">
-        <v>0.7857142857142857</v>
+        <v>0.7998338870431894</v>
       </c>
       <c r="D32" t="n">
         <v>0.6666666666666666</v>
       </c>
       <c r="E32" t="n">
-        <v>0.1190476190476191</v>
+        <v>0.1331672203765227</v>
       </c>
     </row>
     <row r="33">
@@ -1149,13 +1149,13 @@
         <v>-0.194595351118395</v>
       </c>
       <c r="C33" t="n">
-        <v>0.2452934662236988</v>
+        <v>0.2884615384615384</v>
       </c>
       <c r="D33" t="n">
         <v>0.4</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.1547065337763013</v>
+        <v>-0.1115384615384616</v>
       </c>
     </row>
     <row r="34">
@@ -1187,13 +1187,13 @@
         <v>-0.226134911817538</v>
       </c>
       <c r="C35" t="n">
-        <v>0.8418604651162791</v>
+        <v>0.9615384615384616</v>
       </c>
       <c r="D35" t="n">
-        <v>0.9285714285714286</v>
+        <v>0.9259259259259259</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.0867109634551495</v>
+        <v>0.03561253561253563</v>
       </c>
     </row>
     <row r="36">
@@ -1206,13 +1206,13 @@
         <v>-0.222738672149269</v>
       </c>
       <c r="C36" t="n">
-        <v>0.1904761904761905</v>
+        <v>0.2870879120879121</v>
       </c>
       <c r="D36" t="n">
-        <v>0.3232142857142857</v>
+        <v>0.325</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.1327380952380953</v>
+        <v>-0.03791208791208794</v>
       </c>
     </row>
     <row r="37">
@@ -1263,13 +1263,13 @@
         <v>-0.2418526659406501</v>
       </c>
       <c r="C39" t="n">
-        <v>0.1333333333333333</v>
+        <v>0.2012820512820513</v>
       </c>
       <c r="D39" t="n">
         <v>0.4333333333333333</v>
       </c>
       <c r="E39" t="n">
-        <v>-0.3</v>
+        <v>-0.2320512820512821</v>
       </c>
     </row>
     <row r="40">
@@ -1301,13 +1301,13 @@
         <v>-0.2392060740558485</v>
       </c>
       <c r="C41" t="n">
-        <v>0.7</v>
+        <v>0.643103448275862</v>
       </c>
       <c r="D41" t="n">
         <v>0.6</v>
       </c>
       <c r="E41" t="n">
-        <v>0.09999999999999998</v>
+        <v>0.04310344827586199</v>
       </c>
     </row>
     <row r="42">
@@ -1320,13 +1320,13 @@
         <v>-0.2246998597349494</v>
       </c>
       <c r="C42" t="n">
-        <v>0.5952380952380952</v>
+        <v>0.692970822281167</v>
       </c>
       <c r="D42" t="n">
-        <v>0.7113095238095238</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="E42" t="n">
-        <v>-0.1160714285714286</v>
+        <v>-0.01536251105216635</v>
       </c>
     </row>
     <row r="43">
@@ -1358,13 +1358,13 @@
         <v>-0.1611385731101388</v>
       </c>
       <c r="C44" t="n">
-        <v>0.8</v>
+        <v>0.8069767441860465</v>
       </c>
       <c r="D44" t="n">
         <v>0.6428571428571429</v>
       </c>
       <c r="E44" t="n">
-        <v>0.1571428571428571</v>
+        <v>0.1641196013289036</v>
       </c>
     </row>
   </sheetData>

--- a/results/class_sensitivity/recurrence_vs_hsp90_selectivity.xlsx
+++ b/results/class_sensitivity/recurrence_vs_hsp90_selectivity.xlsx
@@ -446,7 +446,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.4027484143763214</v>
+        <v>0.4396118853890073</v>
       </c>
     </row>
     <row r="4">
@@ -456,7 +456,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.007414613386193692</v>
+        <v>0.003182025053109462</v>
       </c>
     </row>
     <row r="5">
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.08391401629922249</v>
+        <v>0.1224594405650727</v>
       </c>
     </row>
     <row r="8">
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6432836905889364</v>
+        <v>0.678355523653707</v>
       </c>
     </row>
     <row r="9">
@@ -560,13 +560,13 @@
         <v>-0.1786272139903385</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3205128205128205</v>
+        <v>0.2701252236135957</v>
       </c>
       <c r="D2" t="n">
         <v>0.3461538461538461</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.02564102564102566</v>
+        <v>-0.07602862254025045</v>
       </c>
     </row>
     <row r="3">
@@ -598,13 +598,13 @@
         <v>-0.2094323762561981</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6499999999999999</v>
+        <v>0.6821705426356589</v>
       </c>
       <c r="D4" t="n">
         <v>0.5333333333333333</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1166666666666666</v>
+        <v>0.1488372093023256</v>
       </c>
     </row>
     <row r="5">
@@ -674,13 +674,13 @@
         <v>-0.2183080445642374</v>
       </c>
       <c r="C8" t="n">
-        <v>0.6279069767441861</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D8" t="n">
         <v>0.3333333333333333</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2945736434108527</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="9">
@@ -693,13 +693,13 @@
         <v>-0.1662653967408163</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5391472868217054</v>
+        <v>0.5833333333333333</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5172413793103449</v>
+        <v>0.5144346431435445</v>
       </c>
       <c r="E9" t="n">
-        <v>0.02190590751136057</v>
+        <v>0.06889869018978878</v>
       </c>
     </row>
     <row r="10">
@@ -807,13 +807,13 @@
         <v>-0.2082082076743421</v>
       </c>
       <c r="C15" t="n">
-        <v>0.3</v>
+        <v>0.2666666666666667</v>
       </c>
       <c r="D15" t="n">
         <v>0.5</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.2</v>
+        <v>-0.2333333333333333</v>
       </c>
     </row>
     <row r="16">
@@ -864,13 +864,13 @@
         <v>-0.1414054398988475</v>
       </c>
       <c r="C18" t="n">
-        <v>0.7626303127506014</v>
+        <v>0.7655038759689923</v>
       </c>
       <c r="D18" t="n">
         <v>0.4333333333333333</v>
       </c>
       <c r="E18" t="n">
-        <v>0.3292969794172681</v>
+        <v>0.3321705426356589</v>
       </c>
     </row>
     <row r="19">
@@ -883,13 +883,13 @@
         <v>-0.1783653544666676</v>
       </c>
       <c r="C19" t="n">
-        <v>0.7404761904761905</v>
+        <v>0.7670542635658915</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6525044722719142</v>
+        <v>0.6470099667774087</v>
       </c>
       <c r="E19" t="n">
-        <v>0.08797171820427629</v>
+        <v>0.1200442967884827</v>
       </c>
     </row>
     <row r="20">
@@ -902,13 +902,13 @@
         <v>-0.2272999068630794</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2562015503875969</v>
+        <v>0.2238095238095238</v>
       </c>
       <c r="D20" t="n">
         <v>0.3666666666666666</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.1104651162790697</v>
+        <v>-0.1428571428571428</v>
       </c>
     </row>
     <row r="21">
@@ -921,13 +921,13 @@
         <v>-0.2027319592747009</v>
       </c>
       <c r="C21" t="n">
-        <v>0.4418604651162791</v>
+        <v>0.5116279069767442</v>
       </c>
       <c r="D21" t="n">
         <v>0.6333333333333333</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.1914728682170542</v>
+        <v>-0.1217054263565891</v>
       </c>
     </row>
     <row r="22">
@@ -940,13 +940,13 @@
         <v>-0.2357862821744499</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2</v>
+        <v>0.1581395348837209</v>
       </c>
       <c r="D22" t="n">
         <v>0.3571428571428572</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.1571428571428571</v>
+        <v>-0.1990033222591362</v>
       </c>
     </row>
     <row r="23">
@@ -959,13 +959,13 @@
         <v>-0.1928960493937777</v>
       </c>
       <c r="C23" t="n">
-        <v>0.296551724137931</v>
+        <v>0.3761904761904762</v>
       </c>
       <c r="D23" t="n">
         <v>0.4</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.103448275862069</v>
+        <v>-0.02380952380952384</v>
       </c>
     </row>
     <row r="24">
@@ -997,13 +997,13 @@
         <v>-0.1679123265606992</v>
       </c>
       <c r="C25" t="n">
-        <v>0.6511627906976745</v>
+        <v>0.7380952380952381</v>
       </c>
       <c r="D25" t="n">
         <v>0.5</v>
       </c>
       <c r="E25" t="n">
-        <v>0.1511627906976745</v>
+        <v>0.2380952380952381</v>
       </c>
     </row>
     <row r="26">
@@ -1016,13 +1016,13 @@
         <v>-0.2002121226750436</v>
       </c>
       <c r="C26" t="n">
-        <v>0.4775193798449612</v>
+        <v>0.4666666666666667</v>
       </c>
       <c r="D26" t="n">
         <v>0.5666666666666667</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.08914728682170542</v>
+        <v>-0.09999999999999998</v>
       </c>
     </row>
     <row r="27">
@@ -1038,10 +1038,10 @@
         <v>0.2</v>
       </c>
       <c r="D27" t="n">
-        <v>0.4642857142857143</v>
+        <v>0.4636243386243386</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.2642857142857143</v>
+        <v>-0.2636243386243386</v>
       </c>
     </row>
     <row r="28">
@@ -1111,13 +1111,13 @@
         <v>-0.205184187788136</v>
       </c>
       <c r="C31" t="n">
-        <v>0.7666666666666667</v>
+        <v>0.7674418604651163</v>
       </c>
       <c r="D31" t="n">
         <v>0.5769230769230769</v>
       </c>
       <c r="E31" t="n">
-        <v>0.1897435897435898</v>
+        <v>0.1905187835420394</v>
       </c>
     </row>
     <row r="32">
@@ -1130,13 +1130,13 @@
         <v>-0.184285453771279</v>
       </c>
       <c r="C32" t="n">
-        <v>0.7998338870431894</v>
+        <v>0.7761904761904762</v>
       </c>
       <c r="D32" t="n">
         <v>0.6666666666666666</v>
       </c>
       <c r="E32" t="n">
-        <v>0.1331672203765227</v>
+        <v>0.1095238095238096</v>
       </c>
     </row>
     <row r="33">
@@ -1149,13 +1149,13 @@
         <v>-0.194595351118395</v>
       </c>
       <c r="C33" t="n">
-        <v>0.2884615384615384</v>
+        <v>0.2666666666666667</v>
       </c>
       <c r="D33" t="n">
         <v>0.4</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.1115384615384616</v>
+        <v>-0.1333333333333334</v>
       </c>
     </row>
     <row r="34">
@@ -1168,13 +1168,13 @@
         <v>-0.2238031966272546</v>
       </c>
       <c r="C34" t="n">
-        <v>0.2093023255813954</v>
+        <v>0.2008050089445438</v>
       </c>
       <c r="D34" t="n">
         <v>0.3333333333333333</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.124031007751938</v>
+        <v>-0.1325283243887895</v>
       </c>
     </row>
     <row r="35">
@@ -1187,13 +1187,13 @@
         <v>-0.226134911817538</v>
       </c>
       <c r="C35" t="n">
-        <v>0.9615384615384616</v>
+        <v>0.8837209302325582</v>
       </c>
       <c r="D35" t="n">
-        <v>0.9259259259259259</v>
+        <v>0.9285714285714286</v>
       </c>
       <c r="E35" t="n">
-        <v>0.03561253561253563</v>
+        <v>-0.04485049833887045</v>
       </c>
     </row>
     <row r="36">
@@ -1206,13 +1206,13 @@
         <v>-0.222738672149269</v>
       </c>
       <c r="C36" t="n">
-        <v>0.2870879120879121</v>
+        <v>0.2380952380952381</v>
       </c>
       <c r="D36" t="n">
-        <v>0.325</v>
+        <v>0.3214285714285715</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.03791208791208794</v>
+        <v>-0.08333333333333337</v>
       </c>
     </row>
     <row r="37">
@@ -1263,13 +1263,13 @@
         <v>-0.2418526659406501</v>
       </c>
       <c r="C39" t="n">
-        <v>0.2012820512820513</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="D39" t="n">
         <v>0.4333333333333333</v>
       </c>
       <c r="E39" t="n">
-        <v>-0.2320512820512821</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="40">
@@ -1301,13 +1301,13 @@
         <v>-0.2392060740558485</v>
       </c>
       <c r="C41" t="n">
-        <v>0.643103448275862</v>
+        <v>0.7</v>
       </c>
       <c r="D41" t="n">
         <v>0.6</v>
       </c>
       <c r="E41" t="n">
-        <v>0.04310344827586199</v>
+        <v>0.09999999999999998</v>
       </c>
     </row>
     <row r="42">
@@ -1320,13 +1320,13 @@
         <v>-0.2246998597349494</v>
       </c>
       <c r="C42" t="n">
-        <v>0.692970822281167</v>
+        <v>0.680952380952381</v>
       </c>
       <c r="D42" t="n">
         <v>0.7083333333333334</v>
       </c>
       <c r="E42" t="n">
-        <v>-0.01536251105216635</v>
+        <v>-0.02738095238095239</v>
       </c>
     </row>
     <row r="43">
